--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängsmark O Lockhyttan, Vstm</t>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 217-2024 artfynd.xlsx
+++ b/artfynd/S 217-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150539</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
